--- a/Evaluación-fase-1/RBS Bomberos.xlsx
+++ b/Evaluación-fase-1/RBS Bomberos.xlsx
@@ -286,7 +286,7 @@
     <t>Diferencias entre desarrollo y producción, variables de entorno mal configuradas o servicios necesarios no iniciados correctamente.</t>
   </si>
   <si>
-    <t>1.9 Riesgos Externos e Institucionales</t>
+    <t>1.9 Riesgos Externos y Institucionales</t>
   </si>
   <si>
     <t>1.9.1 Baja disponibilidad de personal de Bomberos para validar</t>
@@ -301,7 +301,7 @@
     <t>Modificaciones en responsables, procedimientos o forma de administrar inventario y mantenimiento durante el desarrollo del proyecto.</t>
   </si>
   <si>
-    <t>1.9.3 Información institucional entregada fuera de plazo</t>
+    <t>1.9.3 Información de Bomberos entregada fuera de plazo</t>
   </si>
   <si>
     <t>Demora en recibir planillas, reglas, datos, accesos o antecedentes necesarios para desarrollar y validar funcionalidades.</t>
@@ -392,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -418,6 +418,12 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1233,7 +1239,7 @@
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="5"/>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -1245,7 +1251,7 @@
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="6"/>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -1257,10 +1263,10 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="6"/>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D44" s="6" t="s">
@@ -1269,7 +1275,7 @@
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="6"/>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C45" s="6" t="s">
